--- a/data/BDD.xlsx
+++ b/data/BDD.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timda\PycharmProjects\Macro-financial-index\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6468b3e9d8abaf9d/MQDE/S1/ML/Macro-financial-index/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2112B16B-D38F-426A-834E-F89290F6EDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00017F84-697F-B548-A53F-8F72578B27A4}"/>
+    <workbookView xWindow="22965" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00017F84-697F-B548-A53F-8F72578B27A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Database" sheetId="1" r:id="rId1"/>
@@ -620,15 +620,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F821043-6BE6-8044-A7AD-A759B548839C}">
   <dimension ref="A1:BJ311"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="2" customWidth="1"/>
     <col min="38" max="40" width="11" customWidth="1"/>
-    <col min="55" max="55" width="10.875" customWidth="1"/>
+    <col min="55" max="55" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -816,7 +816,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>36526</v>
       </c>
@@ -977,7 +977,7 @@
         <v>25.51</v>
       </c>
     </row>
-    <row r="3" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>36557</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>27.78</v>
       </c>
     </row>
-    <row r="4" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>36586</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>27.49</v>
       </c>
     </row>
-    <row r="5" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>36617</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>22.76</v>
       </c>
     </row>
-    <row r="6" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>36647</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>27.74</v>
       </c>
     </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>36678</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="8" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>36708</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>28.68</v>
       </c>
     </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>36739</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>36770</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>33.14</v>
       </c>
     </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>36800</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>30.96</v>
       </c>
     </row>
-    <row r="12" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>36831</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>32.549999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>36861</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>25.66</v>
       </c>
     </row>
-    <row r="14" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>36892</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>25.62</v>
       </c>
     </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>36923</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="16" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>36951</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>36982</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>25.66</v>
       </c>
     </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>37012</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>28.31</v>
       </c>
     </row>
-    <row r="19" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>37043</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>27.85</v>
       </c>
     </row>
-    <row r="20" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>37073</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>24.61</v>
       </c>
     </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>37104</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>25.68</v>
       </c>
     </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>37135</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>25.62</v>
       </c>
     </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>37165</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>20.54</v>
       </c>
     </row>
-    <row r="24" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>37196</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="25" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <v>37226</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>18.71</v>
       </c>
     </row>
-    <row r="26" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>37257</v>
       </c>
@@ -4841,7 +4841,7 @@
         <v>19.420000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>37288</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>20.28</v>
       </c>
     </row>
-    <row r="28" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>37316</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="29" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>37347</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>25.73</v>
       </c>
     </row>
-    <row r="30" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>37377</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>25.35</v>
       </c>
     </row>
-    <row r="31" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>37408</v>
       </c>
@@ -5646,7 +5646,7 @@
         <v>24.08</v>
       </c>
     </row>
-    <row r="32" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>37438</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>25.74</v>
       </c>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A33" s="1">
         <v>37469</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>26.65</v>
       </c>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A34" s="1">
         <v>37500</v>
       </c>
@@ -6129,7 +6129,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="35" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A35" s="1">
         <v>37530</v>
       </c>
@@ -6290,7 +6290,7 @@
         <v>27.54</v>
       </c>
     </row>
-    <row r="36" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A36" s="1">
         <v>37561</v>
       </c>
@@ -6451,7 +6451,7 @@
         <v>24.34</v>
       </c>
     </row>
-    <row r="37" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A37" s="1">
         <v>37591</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>28.33</v>
       </c>
     </row>
-    <row r="38" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A38" s="1">
         <v>37622</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>31.18</v>
       </c>
     </row>
-    <row r="39" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A39" s="1">
         <v>37653</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>32.770000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A40" s="1">
         <v>37681</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>30.61</v>
       </c>
     </row>
-    <row r="41" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A41" s="1">
         <v>37712</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>25.07</v>
       </c>
     </row>
-    <row r="42" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A42" s="1">
         <v>37742</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>25.86</v>
       </c>
     </row>
-    <row r="43" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A43" s="1">
         <v>37773</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>27.65</v>
       </c>
     </row>
-    <row r="44" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A44" s="1">
         <v>37803</v>
       </c>
@@ -7739,7 +7739,7 @@
         <v>28.35</v>
       </c>
     </row>
-    <row r="45" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A45" s="1">
         <v>37834</v>
       </c>
@@ -7900,7 +7900,7 @@
         <v>29.89</v>
       </c>
     </row>
-    <row r="46" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A46" s="1">
         <v>37865</v>
       </c>
@@ -8061,7 +8061,7 @@
         <v>27.11</v>
       </c>
     </row>
-    <row r="47" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A47" s="1">
         <v>37895</v>
       </c>
@@ -8222,7 +8222,7 @@
         <v>29.61</v>
       </c>
     </row>
-    <row r="48" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A48" s="1">
         <v>37926</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>28.75</v>
       </c>
     </row>
-    <row r="49" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A49" s="1">
         <v>37956</v>
       </c>
@@ -8544,7 +8544,7 @@
         <v>29.81</v>
       </c>
     </row>
-    <row r="50" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A50" s="1">
         <v>37987</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>31.28</v>
       </c>
     </row>
-    <row r="51" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A51" s="1">
         <v>38018</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>30.86</v>
       </c>
     </row>
-    <row r="52" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A52" s="1">
         <v>38047</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>33.630000000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A53" s="1">
         <v>38078</v>
       </c>
@@ -9188,7 +9188,7 @@
         <v>33.590000000000003</v>
       </c>
     </row>
-    <row r="54" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A54" s="1">
         <v>38108</v>
       </c>
@@ -9349,7 +9349,7 @@
         <v>37.57</v>
       </c>
     </row>
-    <row r="55" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A55" s="1">
         <v>38139</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>35.18</v>
       </c>
     </row>
-    <row r="56" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A56" s="1">
         <v>38169</v>
       </c>
@@ -9671,7 +9671,7 @@
         <v>38.22</v>
       </c>
     </row>
-    <row r="57" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A57" s="1">
         <v>38200</v>
       </c>
@@ -9832,7 +9832,7 @@
         <v>42.74</v>
       </c>
     </row>
-    <row r="58" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A58" s="3">
         <v>38231</v>
       </c>
@@ -10017,7 +10017,7 @@
         <v>43.2</v>
       </c>
     </row>
-    <row r="59" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A59" s="1">
         <v>38261</v>
       </c>
@@ -10202,7 +10202,7 @@
         <v>49.78</v>
       </c>
     </row>
-    <row r="60" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A60" s="1">
         <v>38292</v>
       </c>
@@ -10387,7 +10387,7 @@
         <v>43.11</v>
       </c>
     </row>
-    <row r="61" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A61" s="1">
         <v>38322</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>39.6</v>
       </c>
     </row>
-    <row r="62" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A62" s="1">
         <v>38353</v>
       </c>
@@ -10757,7 +10757,7 @@
         <v>44.51</v>
       </c>
     </row>
-    <row r="63" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A63" s="1">
         <v>38384</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>45.48</v>
       </c>
     </row>
-    <row r="64" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A64" s="1">
         <v>38412</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="65" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A65" s="1">
         <v>38443</v>
       </c>
@@ -11312,7 +11312,7 @@
         <v>51.88</v>
       </c>
     </row>
-    <row r="66" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A66" s="1">
         <v>38473</v>
       </c>
@@ -11497,7 +11497,7 @@
         <v>48.65</v>
       </c>
     </row>
-    <row r="67" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A67" s="1">
         <v>38504</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>54.35</v>
       </c>
     </row>
-    <row r="68" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A68" s="1">
         <v>38534</v>
       </c>
@@ -11867,7 +11867,7 @@
         <v>57.52</v>
       </c>
     </row>
-    <row r="69" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A69" s="1">
         <v>38565</v>
       </c>
@@ -12052,7 +12052,7 @@
         <v>63.98</v>
       </c>
     </row>
-    <row r="70" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A70" s="1">
         <v>38596</v>
       </c>
@@ -12237,7 +12237,7 @@
         <v>62.91</v>
       </c>
     </row>
-    <row r="71" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A71" s="1">
         <v>38626</v>
       </c>
@@ -12422,7 +12422,7 @@
         <v>58.54</v>
       </c>
     </row>
-    <row r="72" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A72" s="1">
         <v>38657</v>
       </c>
@@ -12607,7 +12607,7 @@
         <v>55.24</v>
       </c>
     </row>
-    <row r="73" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A73" s="1">
         <v>38687</v>
       </c>
@@ -12792,7 +12792,7 @@
         <v>56.86</v>
       </c>
     </row>
-    <row r="74" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A74" s="1">
         <v>38718</v>
       </c>
@@ -12977,7 +12977,7 @@
         <v>62.99</v>
       </c>
     </row>
-    <row r="75" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A75" s="1">
         <v>38749</v>
       </c>
@@ -13162,7 +13162,7 @@
         <v>60.21</v>
       </c>
     </row>
-    <row r="76" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A76" s="1">
         <v>38777</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>62.06</v>
       </c>
     </row>
-    <row r="77" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A77" s="1">
         <v>38808</v>
       </c>
@@ -13532,7 +13532,7 @@
         <v>70.260000000000005</v>
       </c>
     </row>
-    <row r="78" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A78" s="1">
         <v>38838</v>
       </c>
@@ -13717,7 +13717,7 @@
         <v>69.78</v>
       </c>
     </row>
-    <row r="79" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A79" s="1">
         <v>38869</v>
       </c>
@@ -13902,7 +13902,7 @@
         <v>68.56</v>
       </c>
     </row>
-    <row r="80" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A80" s="1">
         <v>38899</v>
       </c>
@@ -14087,7 +14087,7 @@
         <v>73.67</v>
       </c>
     </row>
-    <row r="81" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A81" s="1">
         <v>38930</v>
       </c>
@@ -14272,7 +14272,7 @@
         <v>73.23</v>
       </c>
     </row>
-    <row r="82" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A82" s="1">
         <v>38961</v>
       </c>
@@ -14457,7 +14457,7 @@
         <v>61.96</v>
       </c>
     </row>
-    <row r="83" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A83" s="1">
         <v>38991</v>
       </c>
@@ -14642,7 +14642,7 @@
         <v>57.81</v>
       </c>
     </row>
-    <row r="84" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A84" s="1">
         <v>39022</v>
       </c>
@@ -14827,7 +14827,7 @@
         <v>58.76</v>
       </c>
     </row>
-    <row r="85" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A85" s="1">
         <v>39052</v>
       </c>
@@ -15012,7 +15012,7 @@
         <v>62.47</v>
       </c>
     </row>
-    <row r="86" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A86" s="1">
         <v>39083</v>
       </c>
@@ -15197,7 +15197,7 @@
         <v>53.68</v>
       </c>
     </row>
-    <row r="87" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A87" s="1">
         <v>39114</v>
       </c>
@@ -15382,7 +15382,7 @@
         <v>57.56</v>
       </c>
     </row>
-    <row r="88" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A88" s="1">
         <v>39142</v>
       </c>
@@ -15570,7 +15570,7 @@
         <v>62.05</v>
       </c>
     </row>
-    <row r="89" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A89" s="1">
         <v>39173</v>
       </c>
@@ -15758,7 +15758,7 @@
         <v>67.489999999999995</v>
       </c>
     </row>
-    <row r="90" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A90" s="1">
         <v>39203</v>
       </c>
@@ -15946,7 +15946,7 @@
         <v>67.209999999999994</v>
       </c>
     </row>
-    <row r="91" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A91" s="1">
         <v>39234</v>
       </c>
@@ -16134,7 +16134,7 @@
         <v>71.05</v>
       </c>
     </row>
-    <row r="92" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A92" s="1">
         <v>39264</v>
       </c>
@@ -16322,7 +16322,7 @@
         <v>76.930000000000007</v>
       </c>
     </row>
-    <row r="93" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A93" s="1">
         <v>39295</v>
       </c>
@@ -16510,7 +16510,7 @@
         <v>70.760000000000005</v>
       </c>
     </row>
-    <row r="94" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A94" s="1">
         <v>39326</v>
       </c>
@@ -16698,7 +16698,7 @@
         <v>77.17</v>
       </c>
     </row>
-    <row r="95" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A95" s="1">
         <v>39356</v>
       </c>
@@ -16886,7 +16886,7 @@
         <v>82.34</v>
       </c>
     </row>
-    <row r="96" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A96" s="1">
         <v>39387</v>
       </c>
@@ -17074,7 +17074,7 @@
         <v>92.41</v>
       </c>
     </row>
-    <row r="97" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A97" s="1">
         <v>39417</v>
       </c>
@@ -17262,7 +17262,7 @@
         <v>90.93</v>
       </c>
     </row>
-    <row r="98" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A98" s="1">
         <v>39448</v>
       </c>
@@ -17450,7 +17450,7 @@
         <v>92.18</v>
       </c>
     </row>
-    <row r="99" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A99" s="1">
         <v>39479</v>
       </c>
@@ -17638,7 +17638,7 @@
         <v>94.99</v>
       </c>
     </row>
-    <row r="100" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A100" s="1">
         <v>39508</v>
       </c>
@@ -17826,7 +17826,7 @@
         <v>103.64</v>
       </c>
     </row>
-    <row r="101" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A101" s="1">
         <v>39539</v>
       </c>
@@ -18014,7 +18014,7 @@
         <v>109.07</v>
       </c>
     </row>
-    <row r="102" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A102" s="1">
         <v>39569</v>
       </c>
@@ -18202,7 +18202,7 @@
         <v>122.8</v>
       </c>
     </row>
-    <row r="103" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A103" s="1">
         <v>39600</v>
       </c>
@@ -18390,7 +18390,7 @@
         <v>132.32</v>
       </c>
     </row>
-    <row r="104" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A104" s="1">
         <v>39630</v>
       </c>
@@ -18578,7 +18578,7 @@
         <v>132.72</v>
       </c>
     </row>
-    <row r="105" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A105" s="1">
         <v>39661</v>
       </c>
@@ -18766,7 +18766,7 @@
         <v>113.24</v>
       </c>
     </row>
-    <row r="106" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A106" s="1">
         <v>39692</v>
       </c>
@@ -18954,7 +18954,7 @@
         <v>97.23</v>
       </c>
     </row>
-    <row r="107" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A107" s="1">
         <v>39722</v>
       </c>
@@ -19142,7 +19142,7 @@
         <v>71.58</v>
       </c>
     </row>
-    <row r="108" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A108" s="1">
         <v>39753</v>
       </c>
@@ -19330,7 +19330,7 @@
         <v>52.45</v>
       </c>
     </row>
-    <row r="109" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A109" s="1">
         <v>39783</v>
       </c>
@@ -19518,7 +19518,7 @@
         <v>39.950000000000003</v>
       </c>
     </row>
-    <row r="110" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A110" s="1">
         <v>39814</v>
       </c>
@@ -19706,7 +19706,7 @@
         <v>43.44</v>
       </c>
     </row>
-    <row r="111" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A111" s="1">
         <v>39845</v>
       </c>
@@ -19894,7 +19894,7 @@
         <v>43.32</v>
       </c>
     </row>
-    <row r="112" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A112" s="1">
         <v>39873</v>
       </c>
@@ -20082,7 +20082,7 @@
         <v>46.54</v>
       </c>
     </row>
-    <row r="113" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A113" s="1">
         <v>39904</v>
       </c>
@@ -20270,7 +20270,7 @@
         <v>50.18</v>
       </c>
     </row>
-    <row r="114" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A114" s="1">
         <v>39934</v>
       </c>
@@ -20458,7 +20458,7 @@
         <v>57.3</v>
       </c>
     </row>
-    <row r="115" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A115" s="1">
         <v>39965</v>
       </c>
@@ -20646,7 +20646,7 @@
         <v>68.61</v>
       </c>
     </row>
-    <row r="116" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A116" s="1">
         <v>39995</v>
       </c>
@@ -20834,7 +20834,7 @@
         <v>64.44</v>
       </c>
     </row>
-    <row r="117" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A117" s="1">
         <v>40026</v>
       </c>
@@ -21022,7 +21022,7 @@
         <v>72.510000000000005</v>
       </c>
     </row>
-    <row r="118" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A118" s="1">
         <v>40057</v>
       </c>
@@ -21210,7 +21210,7 @@
         <v>67.650000000000006</v>
       </c>
     </row>
-    <row r="119" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A119" s="1">
         <v>40087</v>
       </c>
@@ -21398,7 +21398,7 @@
         <v>72.77</v>
       </c>
     </row>
-    <row r="120" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A120" s="1">
         <v>40118</v>
       </c>
@@ -21586,7 +21586,7 @@
         <v>76.66</v>
       </c>
     </row>
-    <row r="121" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A121" s="1">
         <v>40148</v>
       </c>
@@ -21774,7 +21774,7 @@
         <v>74.459999999999994</v>
       </c>
     </row>
-    <row r="122" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A122" s="1">
         <v>40179</v>
       </c>
@@ -21962,7 +21962,7 @@
         <v>76.17</v>
       </c>
     </row>
-    <row r="123" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A123" s="1">
         <v>40210</v>
       </c>
@@ -22150,7 +22150,7 @@
         <v>73.75</v>
       </c>
     </row>
-    <row r="124" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A124" s="1">
         <v>40238</v>
       </c>
@@ -22338,7 +22338,7 @@
         <v>78.83</v>
       </c>
     </row>
-    <row r="125" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A125" s="1">
         <v>40269</v>
       </c>
@@ -22526,7 +22526,7 @@
         <v>84.82</v>
       </c>
     </row>
-    <row r="126" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A126" s="1">
         <v>40299</v>
       </c>
@@ -22714,7 +22714,7 @@
         <v>75.95</v>
       </c>
     </row>
-    <row r="127" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A127" s="1">
         <v>40330</v>
       </c>
@@ -22902,7 +22902,7 @@
         <v>74.760000000000005</v>
       </c>
     </row>
-    <row r="128" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A128" s="1">
         <v>40360</v>
       </c>
@@ -23090,7 +23090,7 @@
         <v>75.58</v>
       </c>
     </row>
-    <row r="129" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A129" s="1">
         <v>40391</v>
       </c>
@@ -23278,7 +23278,7 @@
         <v>77.040000000000006</v>
       </c>
     </row>
-    <row r="130" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A130" s="1">
         <v>40422</v>
       </c>
@@ -23466,7 +23466,7 @@
         <v>77.84</v>
       </c>
     </row>
-    <row r="131" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A131" s="1">
         <v>40452</v>
       </c>
@@ -23654,7 +23654,7 @@
         <v>82.66</v>
       </c>
     </row>
-    <row r="132" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A132" s="1">
         <v>40483</v>
       </c>
@@ -23842,7 +23842,7 @@
         <v>85.27</v>
       </c>
     </row>
-    <row r="133" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A133" s="1">
         <v>40513</v>
       </c>
@@ -24030,7 +24030,7 @@
         <v>91.45</v>
       </c>
     </row>
-    <row r="134" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A134" s="1">
         <v>40544</v>
       </c>
@@ -24218,7 +24218,7 @@
         <v>96.52</v>
       </c>
     </row>
-    <row r="135" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A135" s="1">
         <v>40575</v>
       </c>
@@ -24406,7 +24406,7 @@
         <v>103.72</v>
       </c>
     </row>
-    <row r="136" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A136" s="1">
         <v>40603</v>
       </c>
@@ -24594,7 +24594,7 @@
         <v>114.64</v>
       </c>
     </row>
-    <row r="137" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A137" s="1">
         <v>40634</v>
       </c>
@@ -24782,7 +24782,7 @@
         <v>123.26</v>
       </c>
     </row>
-    <row r="138" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A138" s="1">
         <v>40664</v>
       </c>
@@ -24970,7 +24970,7 @@
         <v>114.99</v>
       </c>
     </row>
-    <row r="139" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A139" s="1">
         <v>40695</v>
       </c>
@@ -25158,7 +25158,7 @@
         <v>113.83</v>
       </c>
     </row>
-    <row r="140" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A140" s="1">
         <v>40725</v>
       </c>
@@ -25346,7 +25346,7 @@
         <v>116.97</v>
       </c>
     </row>
-    <row r="141" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A141" s="1">
         <v>40756</v>
       </c>
@@ -25534,7 +25534,7 @@
         <v>110.22</v>
       </c>
     </row>
-    <row r="142" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A142" s="1">
         <v>40787</v>
       </c>
@@ -25722,7 +25722,7 @@
         <v>112.83</v>
       </c>
     </row>
-    <row r="143" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A143" s="1">
         <v>40817</v>
       </c>
@@ -25910,7 +25910,7 @@
         <v>109.55</v>
       </c>
     </row>
-    <row r="144" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A144" s="1">
         <v>40848</v>
       </c>
@@ -26098,7 +26098,7 @@
         <v>110.77</v>
       </c>
     </row>
-    <row r="145" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A145" s="1">
         <v>40878</v>
       </c>
@@ -26286,7 +26286,7 @@
         <v>107.87</v>
       </c>
     </row>
-    <row r="146" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A146" s="1">
         <v>40909</v>
       </c>
@@ -26474,7 +26474,7 @@
         <v>110.69</v>
       </c>
     </row>
-    <row r="147" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A147" s="1">
         <v>40940</v>
       </c>
@@ -26662,7 +26662,7 @@
         <v>119.33</v>
       </c>
     </row>
-    <row r="148" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A148" s="1">
         <v>40969</v>
       </c>
@@ -26850,7 +26850,7 @@
         <v>125.45</v>
       </c>
     </row>
-    <row r="149" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A149" s="1">
         <v>41000</v>
       </c>
@@ -27038,7 +27038,7 @@
         <v>119.42</v>
       </c>
     </row>
-    <row r="150" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A150" s="1">
         <v>41030</v>
       </c>
@@ -27226,7 +27226,7 @@
         <v>110.34</v>
       </c>
     </row>
-    <row r="151" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A151" s="1">
         <v>41061</v>
       </c>
@@ -27414,7 +27414,7 @@
         <v>95.16</v>
       </c>
     </row>
-    <row r="152" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A152" s="1">
         <v>41091</v>
       </c>
@@ -27602,7 +27602,7 @@
         <v>102.62</v>
       </c>
     </row>
-    <row r="153" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A153" s="1">
         <v>41122</v>
       </c>
@@ -27790,7 +27790,7 @@
         <v>113.36</v>
       </c>
     </row>
-    <row r="154" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A154" s="1">
         <v>41153</v>
       </c>
@@ -27978,7 +27978,7 @@
         <v>112.86</v>
       </c>
     </row>
-    <row r="155" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A155" s="1">
         <v>41183</v>
       </c>
@@ -28166,7 +28166,7 @@
         <v>111.71</v>
       </c>
     </row>
-    <row r="156" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A156" s="1">
         <v>41214</v>
       </c>
@@ -28354,7 +28354,7 @@
         <v>109.06</v>
       </c>
     </row>
-    <row r="157" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A157" s="1">
         <v>41244</v>
       </c>
@@ -28542,7 +28542,7 @@
         <v>109.49</v>
       </c>
     </row>
-    <row r="158" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A158" s="1">
         <v>41275</v>
       </c>
@@ -28730,7 +28730,7 @@
         <v>112.96</v>
       </c>
     </row>
-    <row r="159" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A159" s="1">
         <v>41306</v>
       </c>
@@ -28918,7 +28918,7 @@
         <v>116.05</v>
       </c>
     </row>
-    <row r="160" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A160" s="1">
         <v>41334</v>
       </c>
@@ -29106,7 +29106,7 @@
         <v>108.47</v>
       </c>
     </row>
-    <row r="161" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A161" s="1">
         <v>41365</v>
       </c>
@@ -29294,7 +29294,7 @@
         <v>102.25</v>
       </c>
     </row>
-    <row r="162" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A162" s="1">
         <v>41395</v>
       </c>
@@ -29482,7 +29482,7 @@
         <v>102.56</v>
       </c>
     </row>
-    <row r="163" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A163" s="1">
         <v>41426</v>
       </c>
@@ -29670,7 +29670,7 @@
         <v>102.92</v>
       </c>
     </row>
-    <row r="164" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A164" s="1">
         <v>41456</v>
       </c>
@@ -29858,7 +29858,7 @@
         <v>107.93</v>
       </c>
     </row>
-    <row r="165" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A165" s="1">
         <v>41487</v>
       </c>
@@ -30046,7 +30046,7 @@
         <v>111.28</v>
       </c>
     </row>
-    <row r="166" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A166" s="1">
         <v>41518</v>
       </c>
@@ -30234,7 +30234,7 @@
         <v>111.6</v>
       </c>
     </row>
-    <row r="167" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A167" s="1">
         <v>41548</v>
       </c>
@@ -30422,7 +30422,7 @@
         <v>109.08</v>
       </c>
     </row>
-    <row r="168" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A168" s="1">
         <v>41579</v>
       </c>
@@ -30610,7 +30610,7 @@
         <v>107.79</v>
       </c>
     </row>
-    <row r="169" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A169" s="1">
         <v>41609</v>
       </c>
@@ -30798,7 +30798,7 @@
         <v>110.76</v>
       </c>
     </row>
-    <row r="170" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A170" s="1">
         <v>41640</v>
       </c>
@@ -30986,7 +30986,7 @@
         <v>108.12</v>
       </c>
     </row>
-    <row r="171" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A171" s="1">
         <v>41671</v>
       </c>
@@ -31174,7 +31174,7 @@
         <v>108.9</v>
       </c>
     </row>
-    <row r="172" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A172" s="1">
         <v>41699</v>
       </c>
@@ -31362,7 +31362,7 @@
         <v>107.48</v>
       </c>
     </row>
-    <row r="173" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A173" s="1">
         <v>41730</v>
       </c>
@@ -31550,7 +31550,7 @@
         <v>107.76</v>
       </c>
     </row>
-    <row r="174" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A174" s="1">
         <v>41760</v>
       </c>
@@ -31738,7 +31738,7 @@
         <v>109.54</v>
       </c>
     </row>
-    <row r="175" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A175" s="1">
         <v>41791</v>
       </c>
@@ -31926,7 +31926,7 @@
         <v>111.8</v>
       </c>
     </row>
-    <row r="176" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A176" s="1">
         <v>41821</v>
       </c>
@@ -32114,7 +32114,7 @@
         <v>106.77</v>
       </c>
     </row>
-    <row r="177" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A177" s="1">
         <v>41852</v>
       </c>
@@ -32302,7 +32302,7 @@
         <v>101.61</v>
       </c>
     </row>
-    <row r="178" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A178" s="1">
         <v>41883</v>
       </c>
@@ -32490,7 +32490,7 @@
         <v>97.09</v>
       </c>
     </row>
-    <row r="179" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A179" s="1">
         <v>41913</v>
       </c>
@@ -32678,7 +32678,7 @@
         <v>87.43</v>
       </c>
     </row>
-    <row r="180" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A180" s="1">
         <v>41944</v>
       </c>
@@ -32866,7 +32866,7 @@
         <v>79.44</v>
       </c>
     </row>
-    <row r="181" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A181" s="1">
         <v>41974</v>
       </c>
@@ -33054,7 +33054,7 @@
         <v>62.34</v>
       </c>
     </row>
-    <row r="182" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A182" s="1">
         <v>42005</v>
       </c>
@@ -33242,7 +33242,7 @@
         <v>47.76</v>
       </c>
     </row>
-    <row r="183" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A183" s="1">
         <v>42036</v>
       </c>
@@ -33430,7 +33430,7 @@
         <v>58.1</v>
       </c>
     </row>
-    <row r="184" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A184" s="1">
         <v>42064</v>
       </c>
@@ -33618,7 +33618,7 @@
         <v>55.89</v>
       </c>
     </row>
-    <row r="185" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A185" s="1">
         <v>42095</v>
       </c>
@@ -33806,7 +33806,7 @@
         <v>59.52</v>
       </c>
     </row>
-    <row r="186" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A186" s="1">
         <v>42125</v>
       </c>
@@ -33994,7 +33994,7 @@
         <v>64.08</v>
       </c>
     </row>
-    <row r="187" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A187" s="1">
         <v>42156</v>
       </c>
@@ -34182,7 +34182,7 @@
         <v>61.48</v>
       </c>
     </row>
-    <row r="188" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A188" s="1">
         <v>42186</v>
       </c>
@@ -34370,7 +34370,7 @@
         <v>56.56</v>
       </c>
     </row>
-    <row r="189" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A189" s="1">
         <v>42217</v>
       </c>
@@ -34558,7 +34558,7 @@
         <v>46.52</v>
       </c>
     </row>
-    <row r="190" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A190" s="1">
         <v>42248</v>
       </c>
@@ -34746,7 +34746,7 @@
         <v>47.62</v>
       </c>
     </row>
-    <row r="191" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A191" s="1">
         <v>42278</v>
       </c>
@@ -34934,7 +34934,7 @@
         <v>48.43</v>
       </c>
     </row>
-    <row r="192" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A192" s="1">
         <v>42309</v>
       </c>
@@ -35122,7 +35122,7 @@
         <v>44.27</v>
       </c>
     </row>
-    <row r="193" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A193" s="1">
         <v>42339</v>
       </c>
@@ -35310,7 +35310,7 @@
         <v>38.01</v>
       </c>
     </row>
-    <row r="194" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A194" s="1">
         <v>42370</v>
       </c>
@@ -35498,7 +35498,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="195" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A195" s="1">
         <v>42401</v>
       </c>
@@ -35686,7 +35686,7 @@
         <v>32.18</v>
       </c>
     </row>
-    <row r="196" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A196" s="1">
         <v>42430</v>
       </c>
@@ -35874,7 +35874,7 @@
         <v>38.21</v>
       </c>
     </row>
-    <row r="197" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A197" s="1">
         <v>42461</v>
       </c>
@@ -36062,7 +36062,7 @@
         <v>41.58</v>
       </c>
     </row>
-    <row r="198" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A198" s="1">
         <v>42491</v>
       </c>
@@ -36250,7 +36250,7 @@
         <v>46.74</v>
       </c>
     </row>
-    <row r="199" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A199" s="1">
         <v>42522</v>
       </c>
@@ -36438,7 +36438,7 @@
         <v>48.25</v>
       </c>
     </row>
-    <row r="200" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A200" s="1">
         <v>42552</v>
       </c>
@@ -36626,7 +36626,7 @@
         <v>44.95</v>
       </c>
     </row>
-    <row r="201" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A201" s="1">
         <v>42583</v>
       </c>
@@ -36814,7 +36814,7 @@
         <v>45.84</v>
       </c>
     </row>
-    <row r="202" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A202" s="1">
         <v>42614</v>
       </c>
@@ -37002,7 +37002,7 @@
         <v>46.57</v>
       </c>
     </row>
-    <row r="203" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A203" s="1">
         <v>42644</v>
       </c>
@@ -37190,7 +37190,7 @@
         <v>49.52</v>
       </c>
     </row>
-    <row r="204" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A204" s="1">
         <v>42675</v>
       </c>
@@ -37378,7 +37378,7 @@
         <v>44.73</v>
       </c>
     </row>
-    <row r="205" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A205" s="1">
         <v>42705</v>
       </c>
@@ -37566,7 +37566,7 @@
         <v>53.31</v>
       </c>
     </row>
-    <row r="206" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A206" s="1">
         <v>42736</v>
       </c>
@@ -37754,7 +37754,7 @@
         <v>54.58</v>
       </c>
     </row>
-    <row r="207" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A207" s="1">
         <v>42767</v>
       </c>
@@ -37942,7 +37942,7 @@
         <v>54.87</v>
       </c>
     </row>
-    <row r="208" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A208" s="1">
         <v>42795</v>
       </c>
@@ -38130,7 +38130,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="209" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A209" s="1">
         <v>42826</v>
       </c>
@@ -38318,7 +38318,7 @@
         <v>52.31</v>
       </c>
     </row>
-    <row r="210" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A210" s="1">
         <v>42856</v>
       </c>
@@ -38506,7 +38506,7 @@
         <v>50.33</v>
       </c>
     </row>
-    <row r="211" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A211" s="1">
         <v>42887</v>
       </c>
@@ -38694,7 +38694,7 @@
         <v>46.37</v>
       </c>
     </row>
-    <row r="212" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A212" s="1">
         <v>42917</v>
       </c>
@@ -38882,7 +38882,7 @@
         <v>48.48</v>
       </c>
     </row>
-    <row r="213" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A213" s="1">
         <v>42948</v>
       </c>
@@ -39070,7 +39070,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="214" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A214" s="1">
         <v>42979</v>
       </c>
@@ -39258,7 +39258,7 @@
         <v>56.15</v>
       </c>
     </row>
-    <row r="215" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A215" s="1">
         <v>43009</v>
       </c>
@@ -39446,7 +39446,7 @@
         <v>57.51</v>
       </c>
     </row>
-    <row r="216" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A216" s="1">
         <v>43040</v>
       </c>
@@ -39634,7 +39634,7 @@
         <v>62.71</v>
       </c>
     </row>
-    <row r="217" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A217" s="1">
         <v>43070</v>
       </c>
@@ -39822,7 +39822,7 @@
         <v>64.37</v>
       </c>
     </row>
-    <row r="218" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A218" s="1">
         <v>43101</v>
       </c>
@@ -40010,7 +40010,7 @@
         <v>69.08</v>
       </c>
     </row>
-    <row r="219" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A219" s="1">
         <v>43132</v>
       </c>
@@ -40198,7 +40198,7 @@
         <v>65.319999999999993</v>
       </c>
     </row>
-    <row r="220" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A220" s="1">
         <v>43160</v>
       </c>
@@ -40386,7 +40386,7 @@
         <v>66.02</v>
       </c>
     </row>
-    <row r="221" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A221" s="1">
         <v>43191</v>
       </c>
@@ -40574,7 +40574,7 @@
         <v>72.11</v>
       </c>
     </row>
-    <row r="222" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A222" s="1">
         <v>43221</v>
       </c>
@@ -40762,7 +40762,7 @@
         <v>76.98</v>
       </c>
     </row>
-    <row r="223" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A223" s="1">
         <v>43252</v>
       </c>
@@ -40950,7 +40950,7 @@
         <v>74.400000000000006</v>
       </c>
     </row>
-    <row r="224" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A224" s="1">
         <v>43282</v>
       </c>
@@ -41138,7 +41138,7 @@
         <v>74.25</v>
       </c>
     </row>
-    <row r="225" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A225" s="1">
         <v>43313</v>
       </c>
@@ -41326,7 +41326,7 @@
         <v>72.53</v>
       </c>
     </row>
-    <row r="226" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A226" s="1">
         <v>43344</v>
       </c>
@@ -41514,7 +41514,7 @@
         <v>78.89</v>
       </c>
     </row>
-    <row r="227" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A227" s="1">
         <v>43374</v>
       </c>
@@ -41702,7 +41702,7 @@
         <v>81.03</v>
       </c>
     </row>
-    <row r="228" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A228" s="1">
         <v>43405</v>
       </c>
@@ -41890,7 +41890,7 @@
         <v>64.75</v>
       </c>
     </row>
-    <row r="229" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A229" s="1">
         <v>43435</v>
       </c>
@@ -42078,7 +42078,7 @@
         <v>57.36</v>
       </c>
     </row>
-    <row r="230" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A230" s="1">
         <v>43466</v>
       </c>
@@ -42266,7 +42266,7 @@
         <v>59.41</v>
       </c>
     </row>
-    <row r="231" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A231" s="1">
         <v>43497</v>
       </c>
@@ -42454,7 +42454,7 @@
         <v>63.96</v>
       </c>
     </row>
-    <row r="232" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A232" s="1">
         <v>43525</v>
       </c>
@@ -42642,7 +42642,7 @@
         <v>66.14</v>
       </c>
     </row>
-    <row r="233" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A233" s="1">
         <v>43556</v>
       </c>
@@ -42830,7 +42830,7 @@
         <v>71.23</v>
       </c>
     </row>
-    <row r="234" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A234" s="1">
         <v>43586</v>
       </c>
@@ -43018,7 +43018,7 @@
         <v>71.319999999999993</v>
       </c>
     </row>
-    <row r="235" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A235" s="1">
         <v>43617</v>
       </c>
@@ -43206,7 +43206,7 @@
         <v>64.22</v>
       </c>
     </row>
-    <row r="236" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A236" s="1">
         <v>43647</v>
       </c>
@@ -43394,7 +43394,7 @@
         <v>63.92</v>
       </c>
     </row>
-    <row r="237" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A237" s="1">
         <v>43678</v>
       </c>
@@ -43582,7 +43582,7 @@
         <v>59.04</v>
       </c>
     </row>
-    <row r="238" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A238" s="1">
         <v>43709</v>
       </c>
@@ -43770,7 +43770,7 @@
         <v>62.83</v>
       </c>
     </row>
-    <row r="239" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A239" s="1">
         <v>43739</v>
       </c>
@@ -43958,7 +43958,7 @@
         <v>59.71</v>
       </c>
     </row>
-    <row r="240" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A240" s="1">
         <v>43770</v>
       </c>
@@ -44146,7 +44146,7 @@
         <v>63.21</v>
       </c>
     </row>
-    <row r="241" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A241" s="1">
         <v>43800</v>
       </c>
@@ -44334,7 +44334,7 @@
         <v>67.22</v>
       </c>
     </row>
-    <row r="242" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A242" s="1">
         <v>43831</v>
       </c>
@@ -44522,7 +44522,7 @@
         <v>63.65</v>
       </c>
     </row>
-    <row r="243" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A243" s="1">
         <v>43862</v>
       </c>
@@ -44710,7 +44710,7 @@
         <v>55.66</v>
       </c>
     </row>
-    <row r="244" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A244" s="1">
         <v>43891</v>
       </c>
@@ -44898,7 +44898,7 @@
         <v>32.01</v>
       </c>
     </row>
-    <row r="245" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A245" s="1">
         <v>43922</v>
       </c>
@@ -45086,7 +45086,7 @@
         <v>18.38</v>
       </c>
     </row>
-    <row r="246" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A246" s="1">
         <v>43952</v>
       </c>
@@ -45274,7 +45274,7 @@
         <v>29.38</v>
       </c>
     </row>
-    <row r="247" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A247" s="1">
         <v>43983</v>
       </c>
@@ -45462,7 +45462,7 @@
         <v>40.270000000000003</v>
       </c>
     </row>
-    <row r="248" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A248" s="1">
         <v>44013</v>
       </c>
@@ -45650,7 +45650,7 @@
         <v>43.24</v>
       </c>
     </row>
-    <row r="249" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A249" s="1">
         <v>44044</v>
       </c>
@@ -45838,7 +45838,7 @@
         <v>44.74</v>
       </c>
     </row>
-    <row r="250" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A250" s="1">
         <v>44075</v>
       </c>
@@ -46026,7 +46026,7 @@
         <v>40.909999999999997</v>
       </c>
     </row>
-    <row r="251" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A251" s="1">
         <v>44105</v>
       </c>
@@ -46214,7 +46214,7 @@
         <v>40.19</v>
       </c>
     </row>
-    <row r="252" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A252" s="1">
         <v>44136</v>
       </c>
@@ -46402,7 +46402,7 @@
         <v>42.69</v>
       </c>
     </row>
-    <row r="253" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A253" s="1">
         <v>44166</v>
       </c>
@@ -46590,7 +46590,7 @@
         <v>49.99</v>
       </c>
     </row>
-    <row r="254" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A254" s="1">
         <v>44197</v>
       </c>
@@ -46778,7 +46778,7 @@
         <v>54.77</v>
       </c>
     </row>
-    <row r="255" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A255" s="1">
         <v>44228</v>
       </c>
@@ -46966,7 +46966,7 @@
         <v>62.28</v>
       </c>
     </row>
-    <row r="256" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A256" s="1">
         <v>44256</v>
       </c>
@@ -47154,7 +47154,7 @@
         <v>65.41</v>
       </c>
     </row>
-    <row r="257" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A257" s="1">
         <v>44287</v>
       </c>
@@ -47342,7 +47342,7 @@
         <v>64.81</v>
       </c>
     </row>
-    <row r="258" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A258" s="1">
         <v>44317</v>
       </c>
@@ -47530,7 +47530,7 @@
         <v>68.53</v>
       </c>
     </row>
-    <row r="259" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A259" s="1">
         <v>44348</v>
       </c>
@@ -47718,7 +47718,7 @@
         <v>73.16</v>
       </c>
     </row>
-    <row r="260" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A260" s="1">
         <v>44378</v>
       </c>
@@ -47906,7 +47906,7 @@
         <v>75.17</v>
       </c>
     </row>
-    <row r="261" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A261" s="1">
         <v>44409</v>
       </c>
@@ -48094,7 +48094,7 @@
         <v>70.75</v>
       </c>
     </row>
-    <row r="262" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A262" s="1">
         <v>44440</v>
       </c>
@@ -48282,7 +48282,7 @@
         <v>74.489999999999995</v>
       </c>
     </row>
-    <row r="263" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A263" s="1">
         <v>44470</v>
       </c>
@@ -48470,7 +48470,7 @@
         <v>83.54</v>
       </c>
     </row>
-    <row r="264" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A264" s="1">
         <v>44501</v>
       </c>
@@ -48658,7 +48658,7 @@
         <v>81.05</v>
       </c>
     </row>
-    <row r="265" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A265" s="1">
         <v>44531</v>
       </c>
@@ -48846,7 +48846,7 @@
         <v>74.17</v>
       </c>
     </row>
-    <row r="266" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A266" s="1">
         <v>44562</v>
       </c>
@@ -49034,7 +49034,7 @@
         <v>86.51</v>
       </c>
     </row>
-    <row r="267" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A267" s="1">
         <v>44593</v>
       </c>
@@ -49222,7 +49222,7 @@
         <v>97.13</v>
       </c>
     </row>
-    <row r="268" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A268" s="1">
         <v>44621</v>
       </c>
@@ -49410,7 +49410,7 @@
         <v>117.25</v>
       </c>
     </row>
-    <row r="269" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A269" s="1">
         <v>44652</v>
       </c>
@@ -49598,7 +49598,7 @@
         <v>104.58</v>
       </c>
     </row>
-    <row r="270" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A270" s="1">
         <v>44682</v>
       </c>
@@ -49786,7 +49786,7 @@
         <v>113.34</v>
       </c>
     </row>
-    <row r="271" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A271" s="1">
         <v>44713</v>
       </c>
@@ -49974,7 +49974,7 @@
         <v>122.71</v>
       </c>
     </row>
-    <row r="272" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A272" s="1">
         <v>44743</v>
       </c>
@@ -50162,7 +50162,7 @@
         <v>111.93</v>
       </c>
     </row>
-    <row r="273" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A273" s="1">
         <v>44774</v>
       </c>
@@ -50350,7 +50350,7 @@
         <v>100.45</v>
       </c>
     </row>
-    <row r="274" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A274" s="1">
         <v>44805</v>
       </c>
@@ -50538,7 +50538,7 @@
         <v>89.76</v>
       </c>
     </row>
-    <row r="275" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A275" s="1">
         <v>44835</v>
       </c>
@@ -50726,7 +50726,7 @@
         <v>93.33</v>
       </c>
     </row>
-    <row r="276" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A276" s="1">
         <v>44866</v>
       </c>
@@ -50914,7 +50914,7 @@
         <v>91.42</v>
       </c>
     </row>
-    <row r="277" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A277" s="1">
         <v>44896</v>
       </c>
@@ -51102,7 +51102,7 @@
         <v>80.92</v>
       </c>
     </row>
-    <row r="278" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A278" s="1">
         <v>44927</v>
       </c>
@@ -51290,7 +51290,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="279" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A279" s="1">
         <v>44958</v>
       </c>
@@ -51478,7 +51478,7 @@
         <v>82.59</v>
       </c>
     </row>
-    <row r="280" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A280" s="1">
         <v>44986</v>
       </c>
@@ -51666,7 +51666,7 @@
         <v>78.430000000000007</v>
       </c>
     </row>
-    <row r="281" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A281" s="1">
         <v>45017</v>
       </c>
@@ -51854,7 +51854,7 @@
         <v>84.64</v>
       </c>
     </row>
-    <row r="282" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A282" s="1">
         <v>45047</v>
       </c>
@@ -52042,7 +52042,7 @@
         <v>75.47</v>
       </c>
     </row>
-    <row r="283" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A283" s="1">
         <v>45078</v>
       </c>
@@ -52230,7 +52230,7 @@
         <v>74.84</v>
       </c>
     </row>
-    <row r="284" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A284" s="1">
         <v>45108</v>
       </c>
@@ -52418,7 +52418,7 @@
         <v>80.11</v>
       </c>
     </row>
-    <row r="285" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A285" s="1">
         <v>45139</v>
       </c>
@@ -52606,7 +52606,7 @@
         <v>86.15</v>
       </c>
     </row>
-    <row r="286" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A286" s="1">
         <v>45170</v>
       </c>
@@ -52794,7 +52794,7 @@
         <v>93.72</v>
       </c>
     </row>
-    <row r="287" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A287" s="1">
         <v>45200</v>
       </c>
@@ -52982,7 +52982,7 @@
         <v>90.6</v>
       </c>
     </row>
-    <row r="288" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A288" s="1">
         <v>45231</v>
       </c>
@@ -53170,7 +53170,7 @@
         <v>82.94</v>
       </c>
     </row>
-    <row r="289" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A289" s="1">
         <v>45261</v>
       </c>
@@ -53358,7 +53358,7 @@
         <v>77.63</v>
       </c>
     </row>
-    <row r="290" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A290" s="1">
         <v>45292</v>
       </c>
@@ -53546,7 +53546,7 @@
         <v>80.12</v>
       </c>
     </row>
-    <row r="291" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A291" s="1">
         <v>45323</v>
       </c>
@@ -53734,7 +53734,7 @@
         <v>83.48</v>
       </c>
     </row>
-    <row r="292" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A292" s="1">
         <v>45352</v>
       </c>
@@ -53922,7 +53922,7 @@
         <v>85.41</v>
       </c>
     </row>
-    <row r="293" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A293" s="1">
         <v>45383</v>
       </c>
@@ -54110,7 +54110,7 @@
         <v>89.94</v>
       </c>
     </row>
-    <row r="294" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A294" s="1">
         <v>45413</v>
       </c>
@@ -54298,7 +54298,7 @@
         <v>81.75</v>
       </c>
     </row>
-    <row r="295" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A295" s="1">
         <v>45444</v>
       </c>
@@ -54486,7 +54486,7 @@
         <v>82.25</v>
       </c>
     </row>
-    <row r="296" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A296" s="1">
         <v>45474</v>
       </c>
@@ -54674,7 +54674,7 @@
         <v>85.15</v>
       </c>
     </row>
-    <row r="297" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A297" s="1">
         <v>45505</v>
       </c>
@@ -54862,7 +54862,7 @@
         <v>80.36</v>
       </c>
     </row>
-    <row r="298" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A298" s="1">
         <v>45536</v>
       </c>
@@ -55050,7 +55050,7 @@
         <v>74.02</v>
       </c>
     </row>
-    <row r="299" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A299" s="1">
         <v>45566</v>
       </c>
@@ -55238,7 +55238,7 @@
         <v>75.63</v>
       </c>
     </row>
-    <row r="300" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A300" s="1">
         <v>45597</v>
       </c>
@@ -55426,7 +55426,7 @@
         <v>74.349999999999994</v>
       </c>
     </row>
-    <row r="301" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A301" s="1">
         <v>45627</v>
       </c>
@@ -55614,7 +55614,7 @@
         <v>73.86</v>
       </c>
     </row>
-    <row r="302" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A302" s="1">
         <v>45658</v>
       </c>
@@ -55802,7 +55802,7 @@
         <v>79.27</v>
       </c>
     </row>
-    <row r="303" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A303" s="1">
         <v>45689</v>
       </c>
@@ -55990,7 +55990,7 @@
         <v>75.44</v>
       </c>
     </row>
-    <row r="304" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A304" s="1">
         <v>45717</v>
       </c>
@@ -56178,7 +56178,7 @@
         <v>72.73</v>
       </c>
     </row>
-    <row r="305" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A305" s="1">
         <v>45748</v>
       </c>
@@ -56366,7 +56366,7 @@
         <v>68.13</v>
       </c>
     </row>
-    <row r="306" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A306" s="1">
         <v>45778</v>
       </c>
@@ -56554,7 +56554,7 @@
         <v>64.45</v>
       </c>
     </row>
-    <row r="307" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A307" s="1">
         <v>45809</v>
       </c>
@@ -56742,7 +56742,7 @@
         <v>71.44</v>
       </c>
     </row>
-    <row r="308" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A308" s="1">
         <v>45839</v>
       </c>
@@ -56930,7 +56930,7 @@
         <v>71.040000000000006</v>
       </c>
     </row>
-    <row r="309" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A309" s="1">
         <v>45870</v>
       </c>
@@ -57100,7 +57100,7 @@
         <v>67.87</v>
       </c>
     </row>
-    <row r="310" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A310" s="1">
         <v>45901</v>
       </c>
@@ -57228,7 +57228,7 @@
         <v>67.989999999999995</v>
       </c>
     </row>
-    <row r="311" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A311" s="1">
         <v>45931</v>
       </c>
@@ -57326,9 +57326,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD109B0A-B5D8-407E-92FE-2CCE20B831F0}">
   <dimension ref="A1:AS5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.4">
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
@@ -57462,7 +57462,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -57599,7 +57599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:45" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -57736,7 +57736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.4">
       <c r="B5" s="2"/>
     </row>
   </sheetData>
